--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,468 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124814224</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570279</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6428222</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124814280</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98076</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570299</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6428250</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124814116</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57664</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570311</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6428135</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124814311</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>570279</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6428222</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814280</v>
+        <v>124814116</v>
       </c>
       <c r="B4" t="n">
-        <v>98076</v>
+        <v>57664</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,39 +922,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570299</v>
+        <v>570311</v>
       </c>
       <c r="R4" t="n">
-        <v>6428250</v>
+        <v>6428135</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814116</v>
+        <v>124814280</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>98076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1036,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570311</v>
+        <v>570299</v>
       </c>
       <c r="R5" t="n">
-        <v>6428135</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,6 +1120,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1256,6 +1256,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124834322</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570286</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6428127</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814224</v>
+        <v>124814116</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57664</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,33 +812,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570279</v>
+        <v>570311</v>
       </c>
       <c r="R3" t="n">
-        <v>6428222</v>
+        <v>6428135</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814116</v>
+        <v>124814224</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,33 +926,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R4" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814116</v>
+        <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R3" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1139,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814311</v>
+        <v>124814116</v>
       </c>
       <c r="B6" t="n">
-        <v>57519</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,16 +1160,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,14 +1179,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1191,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570279</v>
+        <v>570311</v>
       </c>
       <c r="R6" t="n">
-        <v>6428222</v>
+        <v>6428135</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,11 +1232,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814311</v>
+        <v>124814224</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -884,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814224</v>
+        <v>124814280</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>98076</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,39 +922,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R4" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,6 +1006,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814280</v>
+        <v>124814311</v>
       </c>
       <c r="B5" t="n">
-        <v>98076</v>
+        <v>57519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1037,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,13 +1115,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814280</v>
+        <v>124814116</v>
       </c>
       <c r="B4" t="n">
-        <v>98076</v>
+        <v>57664</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,39 +922,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570299</v>
+        <v>570311</v>
       </c>
       <c r="R4" t="n">
-        <v>6428250</v>
+        <v>6428135</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B5" t="n">
-        <v>57519</v>
+        <v>98076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1036,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R5" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,17 +1114,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1144,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814116</v>
+        <v>124814311</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
+        <v>57519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,16 +1155,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,14 +1174,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1196,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R6" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,6 +1227,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814224</v>
+        <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814116</v>
+        <v>124814224</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,33 +931,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -962,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R4" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814280</v>
+        <v>124814116</v>
       </c>
       <c r="B5" t="n">
-        <v>98076</v>
+        <v>57664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1041,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570299</v>
+        <v>570311</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428135</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1125,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B6" t="n">
-        <v>57519</v>
+        <v>98076</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,39 +1155,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R6" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,17 +1233,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814224</v>
+        <v>124814116</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57664</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,33 +931,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570279</v>
+        <v>570311</v>
       </c>
       <c r="R4" t="n">
-        <v>6428222</v>
+        <v>6428135</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814116</v>
+        <v>124814224</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,33 +1045,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R5" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814311</v>
+        <v>124814224</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -884,11 +884,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814224</v>
+        <v>124814280</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>98076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1036,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R5" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,6 +1120,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814280</v>
+        <v>124814311</v>
       </c>
       <c r="B6" t="n">
-        <v>98076</v>
+        <v>57519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,39 +1151,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R6" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,13 +1229,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814224</v>
+        <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -884,6 +884,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814116</v>
+        <v>124814280</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>98076</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,39 +927,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>219797</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570311</v>
+        <v>570299</v>
       </c>
       <c r="R4" t="n">
-        <v>6428135</v>
+        <v>6428250</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,6 +1011,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814280</v>
+        <v>124814224</v>
       </c>
       <c r="B5" t="n">
-        <v>98076</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1042,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1082,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1126,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814311</v>
+        <v>124814116</v>
       </c>
       <c r="B6" t="n">
-        <v>57519</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,16 +1160,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,14 +1179,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1191,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570279</v>
+        <v>570311</v>
       </c>
       <c r="R6" t="n">
-        <v>6428222</v>
+        <v>6428135</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,11 +1232,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814280</v>
+        <v>124814116</v>
       </c>
       <c r="B4" t="n">
-        <v>98076</v>
+        <v>57664</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,39 +927,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219797</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570299</v>
+        <v>570311</v>
       </c>
       <c r="R4" t="n">
-        <v>6428250</v>
+        <v>6428135</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814224</v>
+        <v>124814280</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>98076</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1041,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R5" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,6 +1125,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814116</v>
+        <v>124814224</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
+        <v>57761</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,33 +1160,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570311</v>
+        <v>570279</v>
       </c>
       <c r="R6" t="n">
-        <v>6428135</v>
+        <v>6428222</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>98076</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R3" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,17 +886,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814280</v>
+        <v>124814224</v>
       </c>
       <c r="B5" t="n">
-        <v>98076</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1037,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1121,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1144,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814224</v>
+        <v>124814311</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1186,7 +1181,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1232,6 +1227,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814280</v>
+        <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>98076</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R3" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,13 +886,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1139,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B6" t="n">
-        <v>57519</v>
+        <v>98076</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,39 +1155,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R6" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,17 +1233,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R3" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,17 +886,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -918,7 +914,7 @@
         <v>124814116</v>
       </c>
       <c r="B4" t="n">
-        <v>57664</v>
+        <v>57791</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814224</v>
+        <v>124814311</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>57648</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1071,7 +1067,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1117,6 +1113,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814280</v>
+        <v>124814224</v>
       </c>
       <c r="B6" t="n">
-        <v>98076</v>
+        <v>57914</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,39 +1156,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219797</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,13 +1196,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R6" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>124834322</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124814280</v>
+        <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>57648</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570299</v>
+        <v>570279</v>
       </c>
       <c r="R3" t="n">
-        <v>6428250</v>
+        <v>6428222</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,13 +886,17 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trummade och kom nära.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814311</v>
+        <v>124814280</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1041,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>219797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570279</v>
+        <v>570299</v>
       </c>
       <c r="R5" t="n">
-        <v>6428222</v>
+        <v>6428250</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,17 +1119,13 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Trummade och kom nära.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1263,11 +1263,6 @@
       <c r="B7" t="n">
         <v>57632</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,218 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126017451</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103763</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570215</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6428238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126017453</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105439</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6428235</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103763</v>
+        <v>103765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105439</v>
+        <v>105441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105441</v>
+        <v>105445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105445</v>
+        <v>105446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105448</v>
+        <v>105450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105450</v>
+        <v>105454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105454</v>
+        <v>105467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105467</v>
+        <v>105470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>126017451</v>
       </c>
       <c r="B8" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>126017453</v>
       </c>
       <c r="B9" t="n">
-        <v>105470</v>
+        <v>105479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -799,7 +799,12 @@
         <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>57897</v>
+        <v>57648</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14121-2025 artfynd.xlsx
+++ b/artfynd/A 14121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>124089284</v>
       </c>
       <c r="B2" t="n">
-        <v>56821</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,12 +794,7 @@
         <v>124814311</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,32 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124814116</v>
+        <v>124834322</v>
       </c>
       <c r="B4" t="n">
-        <v>57791</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,14 +935,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570311</v>
+        <v>570286</v>
       </c>
       <c r="R4" t="n">
-        <v>6428135</v>
+        <v>6428127</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,44 +1007,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124814280</v>
+        <v>102188013</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219797</v>
+        <v>102018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,24 +1047,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 14121, Dalhem, Sm</t>
+          <t>Rastplats Norr Dalhems kyrka, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570299</v>
+        <v>570240</v>
       </c>
       <c r="R5" t="n">
-        <v>6428250</v>
+        <v>6428010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,12 +1083,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,56 +1107,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jens Morin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Jens Morin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124814224</v>
+        <v>102103002</v>
       </c>
       <c r="B6" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>102020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1182,24 +1158,37 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 14121, Dalhem, Sm</t>
+          <t>100 m S Marieberg, Dalhem, Överum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570279</v>
+        <v>570232</v>
       </c>
       <c r="R6" t="n">
-        <v>6428222</v>
+        <v>6428055</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,78 +1229,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124834322</v>
+        <v>102188014</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>45046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 14121, Dalhem, Sm</t>
+          <t>Rastplats Norr Dalhems kyrka, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570286</v>
+        <v>570244</v>
       </c>
       <c r="R7" t="n">
-        <v>6428127</v>
+        <v>6428011</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1317,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca, regnigt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,44 +1352,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jens Morin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jens Morin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126017451</v>
+        <v>124814224</v>
       </c>
       <c r="B8" t="n">
-        <v>103803</v>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1400,19 +1397,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalhem, Sm</t>
+          <t>A 14121, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570215</v>
+        <v>570279</v>
       </c>
       <c r="R8" t="n">
-        <v>6428238</v>
+        <v>6428222</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,17 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,64 +1461,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126017453</v>
+        <v>124814116</v>
       </c>
       <c r="B9" t="n">
-        <v>105479</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221423</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalhem, Sm</t>
+          <t>A 14121, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570212</v>
+        <v>570311</v>
       </c>
       <c r="R9" t="n">
-        <v>6428235</v>
+        <v>6428135</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,17 +1550,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,15 +1570,337 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124814280</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 14121, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570299</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6428250</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126017453</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570212</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6428235</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126017451</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>570215</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6428238</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
